--- a/_ForDRA/BVSimulationFiles/87.xlsx
+++ b/_ForDRA/BVSimulationFiles/87.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001673151750972763</v>
+        <v>0.003346303501945526</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001943477370468974</v>
+        <v>0.003886954740937948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002213802989965185</v>
+        <v>0.00442760597993037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002484128609461397</v>
+        <v>0.004968257218922793</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0002754454228957608</v>
+        <v>0.005508908457915216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003024779848453819</v>
+        <v>0.006049559696907638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000329510546795003</v>
+        <v>0.00659021093590006</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003565431087446242</v>
+        <v>0.007130862174892484</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003835756706942453</v>
+        <v>0.007671513413884906</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004106082326438665</v>
+        <v>0.00821216465287733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004376407945934876</v>
+        <v>0.008752815891869752</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004646733565431087</v>
+        <v>0.009293467130862175</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004917059184927298</v>
+        <v>0.009834118369854598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000518738480442351</v>
+        <v>0.01037476960884702</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005457710423919721</v>
+        <v>0.01091542084783944</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005728036043415932</v>
+        <v>0.01145607208683186</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005998361662912144</v>
+        <v>0.01199672332582429</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0006268687282408355</v>
+        <v>0.01253737456481671</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006539012901904568</v>
+        <v>0.01307802580380914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006809338521400778</v>
+        <v>0.01361867704280156</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001673151750972763</v>
+        <v>0.003346303501945526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001943477370468974</v>
+        <v>0.003886954740937948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002213802989965185</v>
+        <v>0.00442760597993037</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002484128609461397</v>
+        <v>0.004968257218922793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002754454228957608</v>
+        <v>0.005508908457915216</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003024779848453819</v>
+        <v>0.006049559696907638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000329510546795003</v>
+        <v>0.00659021093590006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003565431087446242</v>
+        <v>0.007130862174892484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003835756706942453</v>
+        <v>0.007671513413884906</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004106082326438665</v>
+        <v>0.00821216465287733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004376407945934876</v>
+        <v>0.008752815891869752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004646733565431087</v>
+        <v>0.009293467130862175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004917059184927298</v>
+        <v>0.009834118369854598</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000518738480442351</v>
+        <v>0.01037476960884702</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005457710423919721</v>
+        <v>0.01091542084783944</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005728036043415932</v>
+        <v>0.01145607208683186</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005998361662912144</v>
+        <v>0.01199672332582429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006268687282408355</v>
+        <v>0.01253737456481671</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006539012901904568</v>
+        <v>0.01307802580380914</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006809338521400778</v>
+        <v>0.01361867704280156</v>
       </c>
     </row>
   </sheetData>
